--- a/Кибер физ/lab 2.xlsx
+++ b/Кибер физ/lab 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filim\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\study\works\Кибер физ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69311568-75AB-4078-8A82-D8EE8E6F9044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F84C8CF-141E-43C5-9334-70B47BD06664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="3" xr2:uid="{72757621-EDCF-4905-8D78-2C1F479B0F99}"/>
+    <workbookView xWindow="4785" yWindow="1260" windowWidth="21600" windowHeight="11505" xr2:uid="{72757621-EDCF-4905-8D78-2C1F479B0F99}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>la</t>
   </si>
@@ -2201,10 +2201,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DC135E6-9034-4EC9-8A77-0FFD7E3D2466}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2212,13 +2212,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>5</v>
       </c>
@@ -2227,10 +2224,7 @@
         <v>1.1666666666666667E-2</v>
       </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <f>(A2*B2)/C2</f>
+        <f>(A2*B2)</f>
         <v>5.8333333333333334E-2</v>
       </c>
     </row>

--- a/Кибер физ/lab 2.xlsx
+++ b/Кибер физ/lab 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\study\works\Кибер физ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programs\Programs\Study\Кибер физ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F84C8CF-141E-43C5-9334-70B47BD06664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8691D725-1A78-4E2A-8A50-286B7DB68272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4785" yWindow="1260" windowWidth="21600" windowHeight="11505" xr2:uid="{72757621-EDCF-4905-8D78-2C1F479B0F99}"/>
+    <workbookView minimized="1" xWindow="4464" yWindow="4140" windowWidth="17280" windowHeight="10152" activeTab="2" xr2:uid="{72757621-EDCF-4905-8D78-2C1F479B0F99}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -90,22 +90,22 @@
     <t>x1</t>
   </si>
   <si>
-    <t>lam_p</t>
+    <t>lam_s</t>
   </si>
   <si>
-    <t>Ap</t>
+    <t>поступающая (Ao)</t>
   </si>
   <si>
-    <t>Ao</t>
+    <t>oбслуженная (As)</t>
   </si>
   <si>
-    <t>Apot</t>
+    <t>lam_o</t>
   </si>
   <si>
-    <t>Aver</t>
+    <t>P</t>
   </si>
   <si>
-    <t>lam_o_and_i</t>
+    <t>потерянная (AL)</t>
   </si>
 </sst>
 </file>
@@ -174,12 +174,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -214,8 +217,8 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -233,27 +236,17 @@
           </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
-          <c:xVal>
+          <c:cat>
             <c:numRef>
               <c:f>'3'!$D$2:$D$41</c:f>
               <c:numCache>
@@ -381,8 +374,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
               <c:f>'3'!$E$2:$E$41</c:f>
               <c:numCache>
@@ -510,7 +503,7 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
+          </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -533,28 +526,18 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
-          <c:xVal>
+          <c:cat>
             <c:numRef>
               <c:f>'3'!$D$2:$D$41</c:f>
               <c:numCache>
@@ -682,8 +665,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
               <c:f>'3'!$F$2:$F$41</c:f>
               <c:numCache>
@@ -811,7 +794,7 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
+          </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -834,28 +817,18 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
-          <c:xVal>
+          <c:cat>
             <c:numRef>
               <c:f>'3'!$D$2:$D$41</c:f>
               <c:numCache>
@@ -983,8 +956,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
               <c:f>'3'!$G$2:$G$41</c:f>
               <c:numCache>
@@ -1112,7 +1085,7 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
+          </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1128,10 +1101,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:smooth val="0"/>
         <c:axId val="646277904"/>
         <c:axId val="651360064"/>
-      </c:scatterChart>
-      <c:valAx>
+      </c:lineChart>
+      <c:catAx>
         <c:axId val="646277904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
@@ -1191,8 +1165,11 @@
         </c:txPr>
         <c:crossAx val="651360064"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
       <c:valAx>
         <c:axId val="651360064"/>
         <c:scaling>
@@ -1253,7 +1230,7 @@
         </c:txPr>
         <c:crossAx val="646277904"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -2202,9 +2179,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DC135E6-9034-4EC9-8A77-0FFD7E3D2466}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2215,7 +2192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5</v>
       </c>
@@ -2236,9 +2213,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A4E6648-2FCC-4763-9722-E9CBD21BDD3B}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -2258,7 +2238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <f>800*8</f>
         <v>6400</v>
@@ -2292,9 +2272,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AFA44CF-4EBD-4744-ACFE-D864B68370A9}">
   <dimension ref="A1:G41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2317,7 +2297,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>5</v>
       </c>
@@ -2344,7 +2324,7 @@
         <v>0.51045834044304694</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -2364,7 +2344,7 @@
         <v>0.76034896355822412</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -2384,7 +2364,7 @@
         <v>0.88268083390574925</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -2404,7 +2384,7 @@
         <v>0.94256738073238266</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -2424,7 +2404,7 @@
         <v>0.97188434025102799</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -2444,7 +2424,7 @@
         <v>0.98623621326694955</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -2464,7 +2444,7 @@
         <v>0.99326205300091452</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2484,7 +2464,7 @@
         <v>0.99670149424406096</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -2504,7 +2484,7 @@
         <v>0.99838524401817941</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -2524,7 +2504,7 @@
         <v>0.99920950967688005</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -2544,7 +2524,7 @@
         <v>0.99961302205535618</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -2564,7 +2544,7 @@
         <v>0.99981055817476716</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -2584,7 +2564,7 @@
         <v>0.99990726033448596</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2604,7 +2584,7 @@
         <v>0.99995460007023751</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -2624,7 +2604,7 @@
         <v>0.99997777484304029</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -2644,7 +2624,7 @@
         <v>0.99998911985977801</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -2664,7 +2644,7 @@
         <v>0.99999467371809958</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -2684,7 +2664,7 @@
         <v>0.99999739256311915</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -2704,7 +2684,7 @@
         <v>0.99999872355102215</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -2724,7 +2704,7 @@
         <v>0.99999937512504911</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D22" s="1">
         <v>21</v>
       </c>
@@ -2741,7 +2721,7 @@
         <v>0.99999969409767953</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D23" s="1">
         <v>22</v>
       </c>
@@ -2758,7 +2738,7 @@
         <v>0.99999985024807037</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D24" s="1">
         <v>23</v>
       </c>
@@ -2775,7 +2755,7 @@
         <v>0.99999992669019189</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D25" s="1">
         <v>24</v>
       </c>
@@ -2792,7 +2772,7 @@
         <v>0.99999996411179481</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D26" s="1">
         <v>25</v>
       </c>
@@ -2809,7 +2789,7 @@
         <v>0.99999998243122845</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D27" s="1">
         <v>26</v>
       </c>
@@ -2826,7 +2806,7 @@
         <v>0.99999999139935447</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D28" s="1">
         <v>27</v>
       </c>
@@ -2843,7 +2823,7 @@
         <v>0.99999999578962573</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D29" s="1">
         <v>28</v>
       </c>
@@ -2860,7 +2840,7 @@
         <v>0.99999999793884642</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D30" s="1">
         <v>29</v>
       </c>
@@ -2877,7 +2857,7 @@
         <v>0.99999999899097947</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D31" s="1">
         <v>30</v>
       </c>
@@ -2894,7 +2874,7 @@
         <v>0.99999999950604235</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D32" s="1">
         <v>31</v>
       </c>
@@ -2911,7 +2891,7 @@
         <v>0.99999999975818721</v>
       </c>
     </row>
-    <row r="33" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D33" s="1">
         <v>32</v>
       </c>
@@ -2928,7 +2908,7 @@
         <v>0.99999999988162258</v>
       </c>
     </row>
-    <row r="34" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D34" s="1">
         <v>33</v>
       </c>
@@ -2945,7 +2925,7 @@
         <v>0.99999999994204936</v>
       </c>
     </row>
-    <row r="35" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D35" s="1">
         <v>34</v>
       </c>
@@ -2962,7 +2942,7 @@
         <v>0.99999999997163069</v>
       </c>
     </row>
-    <row r="36" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D36" s="1">
         <v>35</v>
       </c>
@@ -2979,7 +2959,7 @@
         <v>0.99999999998611211</v>
       </c>
     </row>
-    <row r="37" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D37" s="1">
         <v>36</v>
       </c>
@@ -2996,7 +2976,7 @@
         <v>0.99999999999320133</v>
       </c>
     </row>
-    <row r="38" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D38" s="1">
         <v>37</v>
       </c>
@@ -3013,7 +2993,7 @@
         <v>0.99999999999667177</v>
       </c>
     </row>
-    <row r="39" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D39" s="1">
         <v>38</v>
       </c>
@@ -3030,7 +3010,7 @@
         <v>0.99999999999837064</v>
       </c>
     </row>
-    <row r="40" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D40" s="1">
         <v>39</v>
       </c>
@@ -3047,7 +3027,7 @@
         <v>0.99999999999920242</v>
       </c>
     </row>
-    <row r="41" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D41" s="1">
         <v>40</v>
       </c>
@@ -3074,13 +3054,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75A845BA-3B10-4A8B-A67A-031295F79DDF}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1"/>
+    <col min="7" max="7" width="17.109375" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -3091,10 +3075,10 @@
         <v>16</v>
       </c>
       <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
         <v>17</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
       </c>
       <c r="F1" t="s">
         <v>18</v>
@@ -3103,13 +3087,13 @@
         <v>19</v>
       </c>
       <c r="H1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>7</v>
       </c>

--- a/Кибер физ/lab 2.xlsx
+++ b/Кибер физ/lab 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programs\Programs\Study\Кибер физ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8691D725-1A78-4E2A-8A50-286B7DB68272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC06689-FC4D-433E-8640-6DBB01B29E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4464" yWindow="4140" windowWidth="17280" windowHeight="10152" activeTab="2" xr2:uid="{72757621-EDCF-4905-8D78-2C1F479B0F99}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14160" activeTab="3" xr2:uid="{72757621-EDCF-4905-8D78-2C1F479B0F99}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
